--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="506" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D258C33-39AF-4F76-BDBE-D4D7BC124237}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
+    <workbookView xWindow="10145" yWindow="585" windowWidth="17280" windowHeight="8880" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Proceso" sheetId="9" r:id="rId1"/>
@@ -31,7 +31,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="85" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1617,7 +1617,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="85" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -6205,7 +6205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="68.400000000000006" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>90</v>
       </c>
